--- a/Download/Focus_Positivi_ZP.xlsx
+++ b/Download/Focus_Positivi_ZP.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="18">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -28,13 +28,46 @@
     <t>N</t>
   </si>
   <si>
+    <t>Lazio</t>
+  </si>
+  <si>
     <t>Stato_conservazione_carcassa</t>
   </si>
   <si>
+    <t>Mummificata</t>
+  </si>
+  <si>
+    <t>In decomposizione</t>
+  </si>
+  <si>
+    <t>Fresca</t>
+  </si>
+  <si>
     <t>Eta_descrizione</t>
   </si>
   <si>
     <t>Sesso</t>
+  </si>
+  <si>
+    <t>0-6 mesi (solo premolari)</t>
+  </si>
+  <si>
+    <t>18-30 mesi (2 molari)</t>
+  </si>
+  <si>
+    <t>6-18 mesi (1 molare)</t>
+  </si>
+  <si>
+    <t>Non determinato</t>
+  </si>
+  <si>
+    <t>Oltre 30 mesi (3 molari)</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>M</t>
   </si>
 </sst>
 </file>
@@ -101,10 +134,410 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2"/>
-      <c r="B2"/>
-      <c r="C2" s="2"/>
-      <c r="D2"/>
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2022.0</v>
+      </c>
+      <c r="C2" t="n" s="2">
+        <v>44681.0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2022.0</v>
+      </c>
+      <c r="C3" t="n" s="2">
+        <v>44688.0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2022.0</v>
+      </c>
+      <c r="C4" t="n" s="2">
+        <v>44695.0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2022.0</v>
+      </c>
+      <c r="C5" t="n" s="2">
+        <v>44702.0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2022.0</v>
+      </c>
+      <c r="C6" t="n" s="2">
+        <v>44709.0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2022.0</v>
+      </c>
+      <c r="C7" t="n" s="2">
+        <v>44716.0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2022.0</v>
+      </c>
+      <c r="C8" t="n" s="2">
+        <v>44723.0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2022.0</v>
+      </c>
+      <c r="C9" t="n" s="2">
+        <v>44730.0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2022.0</v>
+      </c>
+      <c r="C10" t="n" s="2">
+        <v>44737.0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2022.0</v>
+      </c>
+      <c r="C11" t="n" s="2">
+        <v>44744.0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2022.0</v>
+      </c>
+      <c r="C12" t="n" s="2">
+        <v>44758.0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2022.0</v>
+      </c>
+      <c r="C13" t="n" s="2">
+        <v>44772.0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2022.0</v>
+      </c>
+      <c r="C14" t="n" s="2">
+        <v>44786.0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2022.0</v>
+      </c>
+      <c r="C15" t="n" s="2">
+        <v>44807.0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2022.0</v>
+      </c>
+      <c r="C16" t="n" s="2">
+        <v>44821.0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="n">
+        <v>2023.0</v>
+      </c>
+      <c r="C17" t="n" s="2">
+        <v>45060.0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2023.0</v>
+      </c>
+      <c r="C18" t="n" s="2">
+        <v>45067.0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="n">
+        <v>2023.0</v>
+      </c>
+      <c r="C19" t="n" s="2">
+        <v>45074.0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2023.0</v>
+      </c>
+      <c r="C20" t="n" s="2">
+        <v>45088.0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2023.0</v>
+      </c>
+      <c r="C21" t="n" s="2">
+        <v>45095.0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>16.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2023.0</v>
+      </c>
+      <c r="C22" t="n" s="2">
+        <v>45102.0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2023.0</v>
+      </c>
+      <c r="C23" t="n" s="2">
+        <v>45109.0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2023.0</v>
+      </c>
+      <c r="C24" t="n" s="2">
+        <v>45116.0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="n">
+        <v>2023.0</v>
+      </c>
+      <c r="C25" t="n" s="2">
+        <v>45123.0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="n">
+        <v>2023.0</v>
+      </c>
+      <c r="C26" t="n" s="2">
+        <v>45144.0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="n">
+        <v>2024.0</v>
+      </c>
+      <c r="C27" t="n" s="2">
+        <v>45362.0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="n">
+        <v>2024.0</v>
+      </c>
+      <c r="C28" t="n" s="2">
+        <v>45453.0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C29" t="n" s="2">
+        <v>46261.0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C30" t="n" s="2">
+        <v>46268.0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -118,15 +551,35 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2"/>
-      <c r="B2"/>
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="n">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="n">
+        <v>47.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="n">
+        <v>44.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -140,19 +593,157 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2"/>
-      <c r="B2"/>
-      <c r="C2"/>
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="n">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="n">
+        <v>22.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="n">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
